--- a/testdata/00-test-plan.xlsx
+++ b/testdata/00-test-plan.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="542">
   <si>
     <t>Step</t>
   </si>
@@ -107,7 +107,7 @@
     <t>Settings › Users &amp; Rights › People › Bulk upload / edit users</t>
   </si>
   <si>
-    <t>29 rows ready (Pooja Batra has two roles). Every password is Test@1234</t>
+    <t>32 rows ready (Pooja Batra has two roles). Every password is Test@1234</t>
   </si>
   <si>
     <t>6</t>
@@ -569,6 +569,30 @@
     <t>P08</t>
   </si>
   <si>
+    <t>Divya Menon</t>
+  </si>
+  <si>
+    <t>divya.menon@test.saltstayz.com</t>
+  </si>
+  <si>
+    <t>whl1</t>
+  </si>
+  <si>
+    <t>Harish Bhat</t>
+  </si>
+  <si>
+    <t>harish.bhat@test.saltstayz.com</t>
+  </si>
+  <si>
+    <t>Tarun Khanna</t>
+  </si>
+  <si>
+    <t>tarun.khanna@test.saltstayz.com</t>
+  </si>
+  <si>
+    <t>whl2</t>
+  </si>
+  <si>
     <t>Karan Kapoor</t>
   </si>
   <si>
@@ -1304,13 +1328,13 @@
     <t>WH-05</t>
   </si>
   <si>
-    <t>Ajay Thakur › Vikram Singh</t>
-  </si>
-  <si>
-    <t>As Ajay (Warehouse Staff) raise a stock order for the warehouse (P08) from V002 Linen. Approve as Vikram.</t>
-  </si>
-  <si>
-    <t>Goes to the Warehouse Manager (Vikram), not the Pre-opening Team; his approval raises the PO. Vikram himself cannot raise at the warehouse; Ajay receives the goods.</t>
+    <t>Ajay Thakur › Divya Menon › Tarun Khanna</t>
+  </si>
+  <si>
+    <t>As Ajay (Warehouse Staff) raise a stock order for the warehouse (P08) from V002 Linen. Approve as Divya (Warehouse Approver L1, Linen), then as Tarun (Warehouse Approver L2). Then raise items of another sub-category as well.</t>
+  </si>
+  <si>
+    <t>Goes to Warehouse Approver L1 for its sub-category (Divya for Linen; Harish, who has none ticked, approves every sub-category), then L2 (Tarun, or Vikram as Warehouse Manager); the L2 approval raises the PO. Items for different L1s split into separate requests. Nobody approves their own warehouse request. Ajay receives the goods.</t>
   </si>
   <si>
     <t>WH-07</t>
@@ -1322,7 +1346,7 @@
     <t>Order Bed sheet double × 600 at P01 Test Stay Sector 29 (stocked at warehouse; the warehouse holds 420). Approve. Then Warehouse › Stock ledger.</t>
   </si>
   <si>
-    <t>The request goes to the Central Warehouse, not a vendor. The ledger shows 600 ordered and 180 short; Vikram ticks it and Raise purchase for shortfall (his request goes to the Cost Controller). He sends the 420 now; the rest stays open on the property's request until it arrives.</t>
+    <t>The request goes to the Central Warehouse, not a vendor. The ledger shows 600 ordered and 180 short; Vikram ticks it and Raise purchase for shortfall (his request goes to Warehouse Approver L1, then L2: Tarun, not himself). He sends the 420 now; the rest stays open on the property's request until it arrives.</t>
   </si>
   <si>
     <t>CH-01</t>
@@ -2866,117 +2890,117 @@
         <v>185</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>186</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="F22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="F24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F25" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>196</v>
+        <v>147</v>
       </c>
       <c r="F26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="F27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -2991,30 +3015,84 @@
         <v>120</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="F29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F30" s="2"/>
+      <c r="F33" s="2"/>
     </row>
   </sheetData>
 </worksheet>
@@ -3034,1524 +3112,1524 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>124</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>127</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>173</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>173</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>161</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>161</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>161</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>161</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>161</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>161</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>161</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>144</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>173</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>173</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>173</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>173</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>138</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>176</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>161</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -4573,186 +4651,186 @@
         <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
